--- a/data/trans_orig/IP19_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP19_R-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30179</t>
+          <t>29738</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46389</t>
+          <t>45867</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24345</t>
+          <t>24253</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39527</t>
+          <t>39418</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59329</t>
+          <t>59011</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80800</t>
+          <t>81119</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>40,18%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57963</t>
+          <t>58485</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74173</t>
+          <t>74614</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58018</t>
+          <t>58127</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>73200</t>
+          <t>73292</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>121098</t>
+          <t>120779</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>142569</t>
+          <t>142887</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,77%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16285</t>
+          <t>16370</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29884</t>
+          <t>29634</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18979</t>
+          <t>19177</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32501</t>
+          <t>32618</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38884</t>
+          <t>38072</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57813</t>
+          <t>58273</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,61%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>57505</t>
+          <t>57755</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>71104</t>
+          <t>71019</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53469</t>
+          <t>53352</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>66991</t>
+          <t>66793</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>115546</t>
+          <t>115086</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>134475</t>
+          <t>135287</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>78,04%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14215</t>
+          <t>13957</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27250</t>
+          <t>26921</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22541</t>
+          <t>21985</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37045</t>
+          <t>37470</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40577</t>
+          <t>41017</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60155</t>
+          <t>59864</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>35,91%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40142</t>
+          <t>40471</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53177</t>
+          <t>53435</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62287</t>
+          <t>61862</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>76791</t>
+          <t>77347</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>106569</t>
+          <t>106860</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>126147</t>
+          <t>125707</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,4%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54044</t>
+          <t>53793</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76625</t>
+          <t>75544</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45091</t>
+          <t>44767</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65141</t>
+          <t>65260</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>102921</t>
+          <t>104390</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>133586</t>
+          <t>132802</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,03%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>123418</t>
+          <t>124499</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>145999</t>
+          <t>146250</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>136933</t>
+          <t>136814</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>156983</t>
+          <t>157307</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>268531</t>
+          <t>269315</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>299196</t>
+          <t>297727</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,04%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27145</t>
+          <t>26658</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42684</t>
+          <t>41874</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34957</t>
+          <t>34737</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>52001</t>
+          <t>52196</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>66538</t>
+          <t>65933</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>88684</t>
+          <t>89592</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,72%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>61436</t>
+          <t>62246</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>76975</t>
+          <t>77462</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>75288</t>
+          <t>75093</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>92332</t>
+          <t>92552</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>142726</t>
+          <t>141818</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>164872</t>
+          <t>165477</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>61,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,51%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17926</t>
+          <t>18655</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31534</t>
+          <t>31377</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13970</t>
+          <t>13956</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25931</t>
+          <t>26079</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35856</t>
+          <t>35799</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>53332</t>
+          <t>53191</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,12%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>43336</t>
+          <t>43493</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>56944</t>
+          <t>56215</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>46461</t>
+          <t>46313</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58422</t>
+          <t>58436</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>93930</t>
+          <t>94071</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>111406</t>
+          <t>111463</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,69%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>183980</t>
+          <t>184863</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>222721</t>
+          <t>224563</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>185316</t>
+          <t>184434</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>222413</t>
+          <t>223350</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>380640</t>
+          <t>383634</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>433333</t>
+          <t>434264</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,83%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>415445</t>
+          <t>413603</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>454186</t>
+          <t>453303</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>462190</t>
+          <t>461253</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>499287</t>
+          <t>500169</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>889436</t>
+          <t>888505</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>942129</t>
+          <t>939135</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>71,0%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26558</t>
+          <t>26535</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41534</t>
+          <t>41681</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17855</t>
+          <t>17010</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31068</t>
+          <t>30710</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47042</t>
+          <t>47367</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67128</t>
+          <t>67476</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,7%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48399</t>
+          <t>48252</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63375</t>
+          <t>63398</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57974</t>
+          <t>58332</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>71187</t>
+          <t>72032</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>111847</t>
+          <t>111499</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>131933</t>
+          <t>131608</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>73,53%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27756</t>
+          <t>27661</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43415</t>
+          <t>42882</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26022</t>
+          <t>26708</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40545</t>
+          <t>41814</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58080</t>
+          <t>57794</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>80062</t>
+          <t>79207</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>41,82%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>49851</t>
+          <t>50384</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>65510</t>
+          <t>65605</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>55592</t>
+          <t>54323</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>70115</t>
+          <t>69429</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>109341</t>
+          <t>110196</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>131323</t>
+          <t>131609</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>69,49%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17781</t>
+          <t>17838</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31445</t>
+          <t>31031</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20681</t>
+          <t>20444</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34692</t>
+          <t>35193</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42424</t>
+          <t>42808</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63104</t>
+          <t>61872</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>35,75%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54712</t>
+          <t>55126</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>68376</t>
+          <t>68319</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52198</t>
+          <t>51697</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>66209</t>
+          <t>66446</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>109943</t>
+          <t>111175</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>130623</t>
+          <t>130239</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,26%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45736</t>
+          <t>46364</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66178</t>
+          <t>67813</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39025</t>
+          <t>38641</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57843</t>
+          <t>58220</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>90976</t>
+          <t>88407</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>119180</t>
+          <t>118189</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,32%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>139930</t>
+          <t>138295</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>160372</t>
+          <t>159744</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>168706</t>
+          <t>168329</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>187524</t>
+          <t>187908</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>313477</t>
+          <t>314468</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>341681</t>
+          <t>344250</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>79,57%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33262</t>
+          <t>33948</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51599</t>
+          <t>52331</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39339</t>
+          <t>39333</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56817</t>
+          <t>57963</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>77304</t>
+          <t>76793</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>102850</t>
+          <t>102964</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,53%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>97570</t>
+          <t>96838</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>115907</t>
+          <t>115221</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>83797</t>
+          <t>82651</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>101275</t>
+          <t>101281</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>186933</t>
+          <t>186819</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>212479</t>
+          <t>212990</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,5%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10780</t>
+          <t>10726</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21727</t>
+          <t>21327</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17073</t>
+          <t>16674</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31266</t>
+          <t>30151</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>30617</t>
+          <t>30756</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>47262</t>
+          <t>48679</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>38,27%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32184</t>
+          <t>32584</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>43131</t>
+          <t>43185</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>42028</t>
+          <t>43143</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>56221</t>
+          <t>56620</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>79943</t>
+          <t>78526</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>96588</t>
+          <t>96449</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>75,82%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>186741</t>
+          <t>187923</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>227296</t>
+          <t>228355</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>185005</t>
+          <t>180681</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>225800</t>
+          <t>221433</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>380831</t>
+          <t>381036</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>438031</t>
+          <t>437311</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,44%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>451248</t>
+          <t>450189</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>491803</t>
+          <t>490621</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>486726</t>
+          <t>491093</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>527521</t>
+          <t>531845</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>953039</t>
+          <t>953759</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1010239</t>
+          <t>1010034</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,61%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21070</t>
+          <t>21650</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35280</t>
+          <t>35901</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20409</t>
+          <t>20019</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34845</t>
+          <t>35362</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45918</t>
+          <t>46181</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67229</t>
+          <t>66567</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,4%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47810</t>
+          <t>47189</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62020</t>
+          <t>61440</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64952</t>
+          <t>64435</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79388</t>
+          <t>79778</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>115658</t>
+          <t>116320</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>136969</t>
+          <t>136706</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>74,75%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27105</t>
+          <t>27504</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42918</t>
+          <t>43715</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31320</t>
+          <t>31226</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48223</t>
+          <t>47408</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>63758</t>
+          <t>62614</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>86729</t>
+          <t>85791</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,27%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>62796</t>
+          <t>61999</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>78609</t>
+          <t>78210</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>64523</t>
+          <t>65338</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>81426</t>
+          <t>81520</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>131731</t>
+          <t>132669</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>154702</t>
+          <t>155846</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>71,34%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16943</t>
+          <t>16620</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28922</t>
+          <t>28439</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13768</t>
+          <t>14434</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27125</t>
+          <t>26871</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34168</t>
+          <t>34206</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52057</t>
+          <t>53198</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>38,75%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32918</t>
+          <t>33401</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44897</t>
+          <t>45220</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48303</t>
+          <t>48557</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61660</t>
+          <t>60994</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>85211</t>
+          <t>84070</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>103100</t>
+          <t>103062</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>75,08%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52281</t>
+          <t>52941</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>75428</t>
+          <t>74106</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45286</t>
+          <t>44749</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65536</t>
+          <t>65803</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>103368</t>
+          <t>104922</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>132988</t>
+          <t>133768</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,79%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>148149</t>
+          <t>149471</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>171296</t>
+          <t>170636</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>145318</t>
+          <t>145051</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>165568</t>
+          <t>166105</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>301443</t>
+          <t>300663</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>331063</t>
+          <t>329509</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>75,85%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28840</t>
+          <t>28774</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45939</t>
+          <t>45514</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27371</t>
+          <t>27330</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44310</t>
+          <t>44256</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61658</t>
+          <t>59822</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>84618</t>
+          <t>85384</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,57%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>90255</t>
+          <t>90680</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>107354</t>
+          <t>107420</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>66,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>98778</t>
+          <t>98832</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>115717</t>
+          <t>115758</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>194664</t>
+          <t>193898</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>217624</t>
+          <t>219460</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>78,58%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13998</t>
+          <t>13995</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25342</t>
+          <t>26015</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14398</t>
+          <t>14122</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27006</t>
+          <t>26246</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>31192</t>
+          <t>31468</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>48471</t>
+          <t>48605</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,7%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>35745</t>
+          <t>35072</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47089</t>
+          <t>47092</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40819</t>
+          <t>41579</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>53427</t>
+          <t>53703</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>80441</t>
+          <t>80307</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>97720</t>
+          <t>97444</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,59%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>187591</t>
+          <t>185002</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>226969</t>
+          <t>223421</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>176357</t>
+          <t>177926</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>218032</t>
+          <t>218476</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>375115</t>
+          <t>375743</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>429924</t>
+          <t>428387</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,01%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>444533</t>
+          <t>448081</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>483911</t>
+          <t>486500</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>491705</t>
+          <t>491261</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>533380</t>
+          <t>531811</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>951315</t>
+          <t>952852</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1006124</t>
+          <t>1005496</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,8%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30090</t>
+          <t>29595</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46992</t>
+          <t>46581</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37556</t>
+          <t>36932</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58845</t>
+          <t>59989</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>71694</t>
+          <t>72964</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>99624</t>
+          <t>99662</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,3%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56244</t>
+          <t>56655</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73146</t>
+          <t>73641</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73521</t>
+          <t>72377</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>94810</t>
+          <t>95434</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>135978</t>
+          <t>135940</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>163908</t>
+          <t>162638</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>69,03%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27328</t>
+          <t>27008</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42127</t>
+          <t>42340</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27228</t>
+          <t>27034</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44599</t>
+          <t>43340</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>60205</t>
+          <t>59361</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81746</t>
+          <t>81940</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>43,07%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>52554</t>
+          <t>52341</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>67353</t>
+          <t>67673</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>50974</t>
+          <t>52233</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>68345</t>
+          <t>68539</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>108508</t>
+          <t>108314</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>130049</t>
+          <t>130893</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,8%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9867</t>
+          <t>10233</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20016</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11579</t>
+          <t>11468</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24500</t>
+          <t>24652</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23955</t>
+          <t>23987</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40921</t>
+          <t>41730</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>36,51%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31004</t>
+          <t>30539</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41153</t>
+          <t>40787</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38787</t>
+          <t>38635</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51708</t>
+          <t>51819</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>73386</t>
+          <t>72577</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>90352</t>
+          <t>90320</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>79,02%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34746</t>
+          <t>36500</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>70084</t>
+          <t>69630</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55151</t>
+          <t>54648</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82703</t>
+          <t>84303</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>96851</t>
+          <t>96498</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>145407</t>
+          <t>145155</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,75%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>143529</t>
+          <t>143983</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>178867</t>
+          <t>177113</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>133739</t>
+          <t>132139</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>161291</t>
+          <t>161794</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>284648</t>
+          <t>284900</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>333204</t>
+          <t>333557</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,56%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19570</t>
+          <t>19209</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>35645</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33491</t>
+          <t>35008</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71035</t>
+          <t>74235</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>59240</t>
+          <t>57789</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>103308</t>
+          <t>99830</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>36,13%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>81494</t>
+          <t>80665</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>96740</t>
+          <t>97101</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>88982</t>
+          <t>85782</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>126526</t>
+          <t>125009</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>173019</t>
+          <t>176497</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>217087</t>
+          <t>218538</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>79,09%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11978</t>
+          <t>11959</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25440</t>
+          <t>25714</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11463</t>
+          <t>10665</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24902</t>
+          <t>23841</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25724</t>
+          <t>25284</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>45220</t>
+          <t>44593</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,03%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>42871</t>
+          <t>42597</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>56333</t>
+          <t>56352</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>46007</t>
+          <t>47068</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>59446</t>
+          <t>60244</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>94001</t>
+          <t>94628</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>113497</t>
+          <t>113937</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,84%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>162400</t>
+          <t>161888</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>210180</t>
+          <t>211572</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>207701</t>
+          <t>209093</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>266842</t>
+          <t>264362</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>384714</t>
+          <t>385142</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>459062</t>
+          <t>463348</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,44%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>436992</t>
+          <t>435600</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>484772</t>
+          <t>485284</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>471752</t>
+          <t>474232</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>530893</t>
+          <t>529501</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>926705</t>
+          <t>922419</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1001053</t>
+          <t>1000625</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,21%</t>
         </is>
       </c>
     </row>
